--- a/deliverables/CNF_Delivery_Planning.xlsx
+++ b/deliverables/CNF_Delivery_Planning.xlsx
@@ -5305,12 +5305,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">API-08/09 reclassify; E-Way extension may leave ABAP scope entirely</t>
+          <t xml:space="preserve">API-08 integration surface</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRADICTED 2026-08-03 - client uses DigiGST (/DIGIGST/INVP), NOT SAP DRC. E-Way extension stated as 'not core SAP'. See D-017, Q-042</t>
+          <t xml:space="preserve">REFINED 2026-08-04 - BOTH present. SAP eDocument framework installed (EDOC_COCKPIT, EDOCUMENT, ZEDOC_DCC_SRV) AND DigiGST supplies India tables (/DIGIGST/OWARD_H-EWBNUMBER). Not either/or. See D-023</t>
         </is>
       </c>
     </row>
@@ -5446,9 +5446,52 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A-14</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backend is S/4HANA 2022 on-premise; landscape DS4/QS4/PS4</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFIED by system observation 2026-08-04. See D-018</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A-15</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Released A2X APIs exist but are NOT activated on this Gateway</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If not activated, custom services are needed where standard would have sufficed</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFIED - only 7 A2X services registered. See Q-045</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:D16"/>
+  <autoFilter ref="A3:D18"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>